--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1321,11 +1321,11 @@
         <v>115756836</v>
       </c>
       <c r="B7" t="n">
-        <v>57173</v>
+        <v>57273</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1321,7 +1321,7 @@
         <v>115756836</v>
       </c>
       <c r="B7" t="n">
-        <v>57273</v>
+        <v>57277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1702,10 +1702,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122358510</v>
+        <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>58052</v>
+        <v>57525</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1714,20 +1714,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358535</v>
+        <v>122358474</v>
       </c>
       <c r="B11" t="n">
-        <v>57525</v>
+        <v>57803</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,35 +1842,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122358474</v>
+        <v>122358510</v>
       </c>
       <c r="B12" t="n">
-        <v>57803</v>
+        <v>58052</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1962,39 +1962,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1321,7 +1321,7 @@
         <v>115756836</v>
       </c>
       <c r="B7" t="n">
-        <v>57282</v>
+        <v>57287</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57525</v>
+        <v>57530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358474</v>
+        <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>57803</v>
+        <v>58057</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1838,39 +1838,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1950,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122358510</v>
+        <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>58052</v>
+        <v>57808</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1962,39 +1962,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1702,10 +1702,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122358535</v>
+        <v>122358474</v>
       </c>
       <c r="B10" t="n">
-        <v>57530</v>
+        <v>57808</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1718,35 +1718,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>103001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1826,10 +1826,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358510</v>
+        <v>122358535</v>
       </c>
       <c r="B11" t="n">
-        <v>58057</v>
+        <v>57530</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1838,20 +1838,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122358474</v>
+        <v>122358510</v>
       </c>
       <c r="B12" t="n">
-        <v>57808</v>
+        <v>58057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1962,39 +1962,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1449,11 +1449,11 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57861</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1463,11 +1463,6 @@
       </c>
       <c r="E8" t="n">
         <v>103018</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Svartvit flugsnappare</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1336,11 +1336,6 @@
       <c r="E7" t="n">
         <v>100082</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Röd glada</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Milvus milvus</t>
@@ -1715,11 +1710,6 @@
       <c r="E10" t="n">
         <v>103001</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Turdus iliacus</t>
@@ -1821,10 +1811,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358535</v>
+        <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>57530</v>
+        <v>58057</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,20 +1823,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Entita</t>
-        </is>
+        <v>103044</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1856,7 +1841,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1945,10 +1930,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122358510</v>
+        <v>122358535</v>
       </c>
       <c r="B12" t="n">
-        <v>58057</v>
+        <v>57530</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,20 +1942,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
+        <v>103020</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1980,7 +1960,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1444,7 +1444,7 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>57861</v>
+        <v>57865</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1458,6 +1458,11 @@
       </c>
       <c r="E8" t="n">
         <v>103018</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1695,7 +1700,7 @@
         <v>122358474</v>
       </c>
       <c r="B10" t="n">
-        <v>57808</v>
+        <v>57812</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1709,6 +1714,11 @@
       </c>
       <c r="E10" t="n">
         <v>103001</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1814,7 +1824,7 @@
         <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>58057</v>
+        <v>58061</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1828,6 +1838,11 @@
       </c>
       <c r="E11" t="n">
         <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1933,7 +1948,7 @@
         <v>122358535</v>
       </c>
       <c r="B12" t="n">
-        <v>57530</v>
+        <v>57534</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1947,6 +1962,11 @@
       </c>
       <c r="E12" t="n">
         <v>103020</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1697,10 +1697,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122358474</v>
+        <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57812</v>
+        <v>57534</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1713,35 +1713,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103001</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1821,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358510</v>
+        <v>122358474</v>
       </c>
       <c r="B11" t="n">
-        <v>58061</v>
+        <v>57812</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,39 +1833,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122358535</v>
+        <v>122358510</v>
       </c>
       <c r="B12" t="n">
-        <v>57534</v>
+        <v>58061</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,20 +1957,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1444,7 +1444,7 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>57865</v>
+        <v>57866</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57534</v>
+        <v>57535</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358474</v>
+        <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>57812</v>
+        <v>58062</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,39 +1833,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122358510</v>
+        <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>58061</v>
+        <v>57813</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,39 +1957,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358510</v>
+        <v>122358474</v>
       </c>
       <c r="B11" t="n">
-        <v>58062</v>
+        <v>57813</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,39 +1833,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122358474</v>
+        <v>122358510</v>
       </c>
       <c r="B12" t="n">
-        <v>57813</v>
+        <v>58062</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,39 +1957,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>103044</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1697,10 +1697,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122358535</v>
+        <v>122358510</v>
       </c>
       <c r="B10" t="n">
-        <v>57535</v>
+        <v>58062</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1709,20 +1709,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358474</v>
+        <v>122358535</v>
       </c>
       <c r="B11" t="n">
-        <v>57813</v>
+        <v>57535</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1837,35 +1837,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>103020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1945,10 +1945,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122358510</v>
+        <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>58062</v>
+        <v>57813</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1957,39 +1957,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1697,10 +1697,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122358510</v>
+        <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>58062</v>
+        <v>57535</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1709,20 +1709,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122358535</v>
+        <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>57535</v>
+        <v>58062</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,20 +1833,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103020</v>
+        <v>103044</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1576,11 +1576,11 @@
         <v>117035474</v>
       </c>
       <c r="B9" t="n">
-        <v>57278</v>
+        <v>57484</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>117035474</v>
       </c>
       <c r="B9" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>117035474</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>57488</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>102393538</v>
       </c>
       <c r="B2" t="n">
-        <v>5107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -732,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613816.8056122803</v>
+        <v>613817</v>
       </c>
       <c r="R2" t="n">
-        <v>6550835.548262889</v>
+        <v>6550835</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -793,12 +788,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -808,12 +803,7 @@
         <v>102150257</v>
       </c>
       <c r="B3" t="n">
-        <v>56355</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -853,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613816.8056122803</v>
+        <v>613817</v>
       </c>
       <c r="R3" t="n">
-        <v>6550835.548262889</v>
+        <v>6550835</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -918,12 +908,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -933,12 +923,7 @@
         <v>106891892</v>
       </c>
       <c r="B4" t="n">
-        <v>56315</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613816.8056122803</v>
+        <v>613817</v>
       </c>
       <c r="R4" t="n">
-        <v>6550835.548262889</v>
+        <v>6550835</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1046,12 +1031,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1061,12 +1046,7 @@
         <v>99137322</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613816.8056122803</v>
+        <v>613817</v>
       </c>
       <c r="R5" t="n">
-        <v>6550835.548262889</v>
+        <v>6550835</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1182,12 +1162,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1197,12 +1177,7 @@
         <v>115546299</v>
       </c>
       <c r="B6" t="n">
-        <v>57792</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1306,12 +1281,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1321,12 +1296,7 @@
         <v>115756836</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,6 +1306,11 @@
       <c r="E7" t="n">
         <v>100082</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Milvus milvus</t>
@@ -1429,12 +1404,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1444,12 +1419,7 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>57995</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1561,12 +1531,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1576,12 +1546,7 @@
         <v>117035474</v>
       </c>
       <c r="B9" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1685,12 +1650,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1700,12 +1665,7 @@
         <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57535</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1809,12 +1769,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1824,12 +1784,7 @@
         <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>58062</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58408</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1933,12 +1888,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1948,12 +1903,7 @@
         <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>57813</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58161</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2057,15 +2007,139 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mats Gärling</t>
+          <t>Mats Grling</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>101539752</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57578</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102117</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jorduggla</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Asio flammeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Älvinge, Köpenhamn, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>613817</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6550835</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gryt</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Jagande några meter ovanför nyslagen vall med snabba vingslag.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mats Grling</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mats Grling</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -788,12 +788,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -803,7 +803,7 @@
         <v>102150257</v>
       </c>
       <c r="B3" t="n">
-        <v>57580</v>
+        <v>57584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,12 +908,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -923,7 +923,7 @@
         <v>106891892</v>
       </c>
       <c r="B4" t="n">
-        <v>57681</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,12 +1031,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
         <v>99137322</v>
       </c>
       <c r="B5" t="n">
-        <v>57728</v>
+        <v>57732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,12 +1162,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1177,7 +1177,7 @@
         <v>115546299</v>
       </c>
       <c r="B6" t="n">
-        <v>58269</v>
+        <v>58273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1281,12 +1281,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
         <v>115756836</v>
       </c>
       <c r="B7" t="n">
-        <v>57668</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1404,12 +1404,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>58212</v>
+        <v>58216</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,12 +1531,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1546,7 +1546,7 @@
         <v>117035474</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,12 +1650,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1665,7 +1665,7 @@
         <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57889</v>
+        <v>57893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1769,12 +1769,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1784,7 +1784,7 @@
         <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>58408</v>
+        <v>58412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1888,12 +1888,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
         <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>58161</v>
+        <v>58165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2007,12 +2007,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2022,7 +2022,7 @@
         <v>101539752</v>
       </c>
       <c r="B13" t="n">
-        <v>57578</v>
+        <v>57582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2131,12 +2131,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mats Grling</t>
+          <t>Mats Gärling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>102150257</v>
       </c>
       <c r="B3" t="n">
-        <v>57584</v>
+        <v>57585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>106891892</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>99137322</v>
       </c>
       <c r="B5" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>115546299</v>
       </c>
       <c r="B6" t="n">
-        <v>58273</v>
+        <v>58274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>115756836</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>58216</v>
+        <v>58217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>117035474</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>58412</v>
+        <v>58413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>58165</v>
+        <v>58166</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>101539752</v>
       </c>
       <c r="B13" t="n">
-        <v>57582</v>
+        <v>57583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>102150257</v>
       </c>
       <c r="B3" t="n">
-        <v>57585</v>
+        <v>57586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>106891892</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>99137322</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>115546299</v>
       </c>
       <c r="B6" t="n">
-        <v>58274</v>
+        <v>58277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>115756836</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>57674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>58217</v>
+        <v>58219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>117035474</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57894</v>
+        <v>57893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>58413</v>
+        <v>58416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>58166</v>
+        <v>58168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>101539752</v>
       </c>
       <c r="B13" t="n">
-        <v>57583</v>
+        <v>57584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>102150257</v>
       </c>
       <c r="B3" t="n">
-        <v>57586</v>
+        <v>57589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>106891892</v>
       </c>
       <c r="B4" t="n">
-        <v>57687</v>
+        <v>57690</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>99137322</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>115546299</v>
       </c>
       <c r="B6" t="n">
-        <v>58277</v>
+        <v>58280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>115756836</v>
       </c>
       <c r="B7" t="n">
-        <v>57674</v>
+        <v>57677</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>58219</v>
+        <v>58222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>117035474</v>
       </c>
       <c r="B9" t="n">
-        <v>57726</v>
+        <v>57729</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>58416</v>
+        <v>58419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>58168</v>
+        <v>58171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>101539752</v>
       </c>
       <c r="B13" t="n">
-        <v>57584</v>
+        <v>57587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 69355-2020 artfynd.xlsx
+++ b/artfynd/A 69355-2020 artfynd.xlsx
@@ -1177,7 +1177,7 @@
         <v>115546299</v>
       </c>
       <c r="B6" t="n">
-        <v>58280</v>
+        <v>58281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>116066072</v>
       </c>
       <c r="B8" t="n">
-        <v>58222</v>
+        <v>58223</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>122358535</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>122358510</v>
       </c>
       <c r="B11" t="n">
-        <v>58419</v>
+        <v>58420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>122358474</v>
       </c>
       <c r="B12" t="n">
-        <v>58171</v>
+        <v>58172</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
